--- a/wwwroot/145/DuplicateTool.xlsx
+++ b/wwwroot/145/DuplicateTool.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
   <si>
     <t>CourseName</t>
   </si>
@@ -69,114 +69,120 @@
     <t>1002</t>
   </si>
   <si>
+    <t>380</t>
+  </si>
+  <si>
+    <t>280</t>
+  </si>
+  <si>
+    <t>25/1155</t>
+  </si>
+  <si>
+    <t>17-02-2026</t>
+  </si>
+  <si>
+    <t>10:00 AM to 01:00 PM</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Smt. Indira Gandhi Rajkiya Mahavidyalaya, Lalganj Mirzapur</t>
+  </si>
+  <si>
+    <t>1003</t>
+  </si>
+  <si>
+    <t>260</t>
+  </si>
+  <si>
+    <t>195</t>
+  </si>
+  <si>
+    <t>Swatantrata Sangram Senani Vshram Singh Rajkiya Mahavidyalaya, Chunar, Mirzapur</t>
+  </si>
+  <si>
+    <t>1004</t>
+  </si>
+  <si>
     <t>340</t>
   </si>
   <si>
-    <t>280</t>
-  </si>
-  <si>
-    <t>25/1155</t>
-  </si>
-  <si>
-    <t>17-02-2026</t>
-  </si>
-  <si>
-    <t>10:00 AM to 01:00 PM</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Smt. Indira Gandhi Rajkiya Mahavidyalaya, Lalganj Mirzapur</t>
-  </si>
-  <si>
-    <t>1003</t>
-  </si>
-  <si>
-    <t>240</t>
-  </si>
-  <si>
-    <t>195</t>
-  </si>
-  <si>
-    <t>Swatantrata Sangram Senani Vshram Singh Rajkiya Mahavidyalaya, Chunar, Mirzapur</t>
-  </si>
-  <si>
-    <t>1004</t>
+    <t>252</t>
+  </si>
+  <si>
+    <t>Lalta Singh Rajkiya Mahila Mahila Mahavidyalaya, Adalhat, Mirzapur</t>
+  </si>
+  <si>
+    <t>1005</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>Narottam Singh Padam Singh Rajkiya Mahavidyalaya, Mangaraha, Mirzapur</t>
+  </si>
+  <si>
+    <t>1007</t>
+  </si>
+  <si>
+    <t>440</t>
+  </si>
+  <si>
+    <t>337</t>
+  </si>
+  <si>
+    <t>K.B. P.G. College, Mirzapur</t>
+  </si>
+  <si>
+    <t>1008</t>
   </si>
   <si>
     <t>320</t>
   </si>
   <si>
-    <t>252</t>
-  </si>
-  <si>
-    <t>Lalta Singh Rajkiya Mahila Mahila Mahavidyalaya, Adalhat, Mirzapur</t>
-  </si>
-  <si>
-    <t>1005</t>
+    <t>238</t>
+  </si>
+  <si>
+    <t>G.D. BINANI P.G. COLLEGE, MIRZAPUR</t>
+  </si>
+  <si>
+    <t>1021</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>Adarsh Janta Mahavidyalaya, Kolna (Chunar) Mirzapur</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>360</t>
+  </si>
+  <si>
+    <t>272</t>
+  </si>
+  <si>
+    <t>Bhau Rao Deoras Rajkiya Mahavidyalaya, Duddhi, Sonebhadra</t>
+  </si>
+  <si>
+    <t>2002</t>
   </si>
   <si>
     <t>120</t>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>Narottam Singh Padam Singh Rajkiya Mahavidyalaya, Mangaraha, Mirzapur</t>
-  </si>
-  <si>
-    <t>1007</t>
-  </si>
-  <si>
-    <t>420</t>
-  </si>
-  <si>
-    <t>337</t>
-  </si>
-  <si>
-    <t>K.B. P.G. College, Mirzapur</t>
-  </si>
-  <si>
-    <t>1008</t>
-  </si>
-  <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>238</t>
-  </si>
-  <si>
-    <t>G.D. BINANI P.G. COLLEGE, MIRZAPUR</t>
-  </si>
-  <si>
-    <t>1021</t>
-  </si>
-  <si>
-    <t>380</t>
-  </si>
-  <si>
-    <t>304</t>
-  </si>
-  <si>
-    <t>Adarsh Janta Mahavidyalaya, Kolna (Chunar) Mirzapur</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>272</t>
-  </si>
-  <si>
-    <t>Bhau Rao Deoras Rajkiya Mahavidyalaya, Duddhi, Sonebhadra</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
     <t>90</t>
   </si>
   <si>
@@ -186,9 +192,6 @@
     <t>2003</t>
   </si>
   <si>
-    <t>260</t>
-  </si>
-  <si>
     <t>212</t>
   </si>
   <si>
@@ -219,6 +222,9 @@
     <t>3001</t>
   </si>
   <si>
+    <t>460</t>
+  </si>
+  <si>
     <t>348</t>
   </si>
   <si>
@@ -316,9 +322,6 @@
   </si>
   <si>
     <t>41</t>
-  </si>
-  <si>
-    <t>20</t>
   </si>
   <si>
     <t>16</t>
@@ -811,10 +814,10 @@
         <v>50</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>20</v>
@@ -844,7 +847,7 @@
         <v>50</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
@@ -855,13 +858,13 @@
         <v>16</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>20</v>
@@ -873,7 +876,7 @@
         <v>22</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>23</v>
@@ -885,13 +888,13 @@
         <v>24</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
@@ -902,13 +905,13 @@
         <v>16</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>20</v>
@@ -920,7 +923,7 @@
         <v>22</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>23</v>
@@ -932,13 +935,13 @@
         <v>24</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
@@ -949,13 +952,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>20</v>
@@ -967,7 +970,7 @@
         <v>22</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>23</v>
@@ -979,13 +982,13 @@
         <v>24</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -996,13 +999,13 @@
         <v>16</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>20</v>
@@ -1014,7 +1017,7 @@
         <v>22</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>23</v>
@@ -1026,13 +1029,13 @@
         <v>24</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14">
@@ -1043,13 +1046,13 @@
         <v>16</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>20</v>
@@ -1061,7 +1064,7 @@
         <v>22</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>23</v>
@@ -1073,13 +1076,13 @@
         <v>24</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15">
@@ -1090,13 +1093,13 @@
         <v>16</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>20</v>
@@ -1108,7 +1111,7 @@
         <v>22</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>23</v>
@@ -1120,13 +1123,13 @@
         <v>24</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16">
@@ -1134,7 +1137,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>17</v>
@@ -1146,10 +1149,10 @@
         <v>19</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>22</v>
@@ -1181,7 +1184,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>26</v>
@@ -1193,10 +1196,10 @@
         <v>28</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>22</v>
@@ -1228,7 +1231,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>30</v>
@@ -1240,10 +1243,10 @@
         <v>32</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>22</v>
@@ -1275,7 +1278,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>34</v>
@@ -1287,10 +1290,10 @@
         <v>36</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>22</v>
@@ -1322,7 +1325,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>38</v>
@@ -1334,10 +1337,10 @@
         <v>40</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>22</v>
@@ -1369,7 +1372,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>42</v>
@@ -1381,10 +1384,10 @@
         <v>44</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>22</v>
@@ -1416,7 +1419,7 @@
         <v>15</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>46</v>
@@ -1428,10 +1431,10 @@
         <v>48</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>22</v>
@@ -1463,22 +1466,22 @@
         <v>15</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>22</v>
@@ -1502,7 +1505,7 @@
         <v>50</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24">
@@ -1510,29 +1513,29 @@
         <v>15</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="J24" s="2" t="s">
         <v>23</v>
       </c>
@@ -1543,13 +1546,13 @@
         <v>24</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25">
@@ -1557,29 +1560,29 @@
         <v>15</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="E25" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="J25" s="2" t="s">
         <v>23</v>
       </c>
@@ -1590,13 +1593,13 @@
         <v>24</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26">
@@ -1604,29 +1607,29 @@
         <v>15</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="J26" s="2" t="s">
         <v>23</v>
       </c>
@@ -1637,13 +1640,13 @@
         <v>24</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27">
@@ -1651,29 +1654,29 @@
         <v>15</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E27" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="J27" s="2" t="s">
         <v>23</v>
       </c>
@@ -1684,13 +1687,13 @@
         <v>24</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28">
@@ -1698,29 +1701,29 @@
         <v>15</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="J28" s="2" t="s">
         <v>23</v>
       </c>
@@ -1731,13 +1734,13 @@
         <v>24</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29">
@@ -1745,46 +1748,46 @@
         <v>15</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F29" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O29" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="O29" s="2" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="30">
@@ -1792,7 +1795,7 @@
         <v>15</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>17</v>
@@ -1804,10 +1807,10 @@
         <v>19</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>22</v>
@@ -1816,7 +1819,7 @@
         <v>17</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>24</v>
@@ -1839,7 +1842,7 @@
         <v>15</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>26</v>
@@ -1851,10 +1854,10 @@
         <v>28</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>22</v>
@@ -1863,7 +1866,7 @@
         <v>26</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>24</v>
@@ -1886,7 +1889,7 @@
         <v>15</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>30</v>
@@ -1898,10 +1901,10 @@
         <v>32</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>22</v>
@@ -1910,7 +1913,7 @@
         <v>30</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>24</v>
@@ -1933,7 +1936,7 @@
         <v>15</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>34</v>
@@ -1945,10 +1948,10 @@
         <v>36</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>22</v>
@@ -1957,7 +1960,7 @@
         <v>34</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>24</v>
@@ -1980,7 +1983,7 @@
         <v>15</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>38</v>
@@ -1992,10 +1995,10 @@
         <v>40</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>22</v>
@@ -2004,7 +2007,7 @@
         <v>38</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>24</v>
@@ -2027,7 +2030,7 @@
         <v>15</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>42</v>
@@ -2039,10 +2042,10 @@
         <v>44</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>22</v>
@@ -2051,7 +2054,7 @@
         <v>42</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>24</v>
@@ -2074,7 +2077,7 @@
         <v>15</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>46</v>
@@ -2086,10 +2089,10 @@
         <v>48</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>22</v>
@@ -2098,7 +2101,7 @@
         <v>30</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>24</v>
@@ -2121,22 +2124,22 @@
         <v>15</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>22</v>
@@ -2145,7 +2148,7 @@
         <v>50</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>24</v>
@@ -2160,7 +2163,7 @@
         <v>50</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38">
@@ -2168,31 +2171,31 @@
         <v>15</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="E38" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I38" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F38" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="J38" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>24</v>
@@ -2201,13 +2204,13 @@
         <v>24</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39">
@@ -2215,31 +2218,31 @@
         <v>15</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="E39" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I39" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F39" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="J39" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>24</v>
@@ -2248,13 +2251,13 @@
         <v>24</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40">
@@ -2262,31 +2265,31 @@
         <v>15</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D40" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="J40" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>24</v>
@@ -2295,13 +2298,13 @@
         <v>24</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="41">
@@ -2309,31 +2312,31 @@
         <v>15</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E41" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I41" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F41" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="J41" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>24</v>
@@ -2342,13 +2345,13 @@
         <v>24</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42">
@@ -2356,31 +2359,31 @@
         <v>15</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E42" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I42" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F42" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="J42" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>24</v>
@@ -2389,13 +2392,13 @@
         <v>24</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43">
@@ -2403,31 +2406,31 @@
         <v>15</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>22</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>24</v>
@@ -2436,13 +2439,13 @@
         <v>24</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="44">
@@ -2450,7 +2453,7 @@
         <v>15</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>17</v>
@@ -2462,10 +2465,10 @@
         <v>19</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>22</v>
@@ -2497,7 +2500,7 @@
         <v>15</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>26</v>
@@ -2509,10 +2512,10 @@
         <v>28</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>22</v>
@@ -2544,7 +2547,7 @@
         <v>15</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>30</v>
@@ -2556,10 +2559,10 @@
         <v>32</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>22</v>
@@ -2591,7 +2594,7 @@
         <v>15</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>34</v>
@@ -2603,10 +2606,10 @@
         <v>36</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>22</v>
@@ -2638,7 +2641,7 @@
         <v>15</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>38</v>
@@ -2650,10 +2653,10 @@
         <v>40</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>22</v>
@@ -2685,7 +2688,7 @@
         <v>15</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>42</v>
@@ -2697,10 +2700,10 @@
         <v>44</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>22</v>
@@ -2732,7 +2735,7 @@
         <v>15</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>46</v>
@@ -2744,10 +2747,10 @@
         <v>48</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>22</v>
@@ -2779,22 +2782,22 @@
         <v>15</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>22</v>
@@ -2818,7 +2821,7 @@
         <v>50</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52">
@@ -2826,29 +2829,29 @@
         <v>15</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="E52" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I52" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F52" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="J52" s="2" t="s">
         <v>23</v>
       </c>
@@ -2859,13 +2862,13 @@
         <v>24</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="53">
@@ -2873,29 +2876,29 @@
         <v>15</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="E53" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I53" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F53" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="J53" s="2" t="s">
         <v>23</v>
       </c>
@@ -2906,13 +2909,13 @@
         <v>24</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="54">
@@ -2920,29 +2923,29 @@
         <v>15</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D54" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I54" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="J54" s="2" t="s">
         <v>23</v>
       </c>
@@ -2953,13 +2956,13 @@
         <v>24</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="55">
@@ -2967,29 +2970,29 @@
         <v>15</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E55" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I55" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F55" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="J55" s="2" t="s">
         <v>23</v>
       </c>
@@ -3000,13 +3003,13 @@
         <v>24</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="56">
@@ -3014,29 +3017,29 @@
         <v>15</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E56" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I56" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F56" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="J56" s="2" t="s">
         <v>23</v>
       </c>
@@ -3047,13 +3050,13 @@
         <v>24</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57">
@@ -3061,28 +3064,28 @@
         <v>15</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>22</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>23</v>
@@ -3094,45 +3097,45 @@
         <v>24</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>50</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>24</v>
@@ -3147,39 +3150,39 @@
         <v>50</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F59" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H59" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>50</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>24</v>
@@ -3194,39 +3197,39 @@
         <v>50</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>50</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>24</v>
@@ -3241,39 +3244,39 @@
         <v>50</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>50</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>24</v>
@@ -3288,33 +3291,33 @@
         <v>50</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>38</v>
@@ -3340,28 +3343,28 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>46</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E63" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F63" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>30</v>
@@ -3387,31 +3390,31 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>23</v>
@@ -3423,39 +3426,39 @@
         <v>24</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>38</v>
@@ -3481,28 +3484,28 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>46</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>30</v>
@@ -3528,31 +3531,31 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B67" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="F67" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>23</v>
@@ -3564,45 +3567,45 @@
         <v>24</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>24</v>
@@ -3622,34 +3625,34 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>46</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>30</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>24</v>
@@ -3669,34 +3672,34 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>24</v>
@@ -3705,45 +3708,45 @@
         <v>24</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>24</v>
@@ -3763,34 +3766,34 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>46</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>30</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>24</v>
@@ -3810,34 +3813,34 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>24</v>
@@ -3846,45 +3849,45 @@
         <v>24</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>24</v>
@@ -3904,34 +3907,34 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>46</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>30</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>24</v>
@@ -3951,34 +3954,34 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>24</v>
@@ -3987,13 +3990,13 @@
         <v>24</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -4385,10 +4388,10 @@
         <v>50</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F9" s="0" t="s">
         <v>20</v>
@@ -4426,13 +4429,13 @@
         <v>16</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F10" s="0" t="s">
         <v>20</v>
@@ -4444,7 +4447,7 @@
         <v>22</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J10" s="0" t="s">
         <v>23</v>
@@ -4456,10 +4459,10 @@
         <v>24</v>
       </c>
       <c r="M10" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N10" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
@@ -4470,13 +4473,13 @@
         <v>16</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F11" s="0" t="s">
         <v>20</v>
@@ -4488,7 +4491,7 @@
         <v>22</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J11" s="0" t="s">
         <v>23</v>
@@ -4500,10 +4503,10 @@
         <v>24</v>
       </c>
       <c r="M11" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N11" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12">
@@ -4514,13 +4517,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F12" s="0" t="s">
         <v>20</v>
@@ -4532,7 +4535,7 @@
         <v>22</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J12" s="0" t="s">
         <v>23</v>
@@ -4544,10 +4547,10 @@
         <v>24</v>
       </c>
       <c r="M12" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N12" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -4558,13 +4561,13 @@
         <v>16</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D13" s="0" t="s">
         <v>43</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F13" s="0" t="s">
         <v>20</v>
@@ -4576,7 +4579,7 @@
         <v>22</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J13" s="0" t="s">
         <v>23</v>
@@ -4588,10 +4591,10 @@
         <v>24</v>
       </c>
       <c r="M13" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N13" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -4602,13 +4605,13 @@
         <v>16</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F14" s="0" t="s">
         <v>20</v>
@@ -4620,7 +4623,7 @@
         <v>22</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J14" s="0" t="s">
         <v>23</v>
@@ -4632,10 +4635,10 @@
         <v>24</v>
       </c>
       <c r="M14" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N14" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -4646,13 +4649,13 @@
         <v>16</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D15" s="0" t="s">
         <v>27</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F15" s="0" t="s">
         <v>20</v>
@@ -4664,7 +4667,7 @@
         <v>22</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J15" s="0" t="s">
         <v>23</v>
@@ -4676,10 +4679,10 @@
         <v>24</v>
       </c>
       <c r="M15" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="N15" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -4687,7 +4690,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>17</v>
@@ -4699,10 +4702,10 @@
         <v>19</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H16" s="0" t="s">
         <v>22</v>
@@ -4731,7 +4734,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>26</v>
@@ -4743,10 +4746,10 @@
         <v>28</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H17" s="0" t="s">
         <v>22</v>
@@ -4775,7 +4778,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>30</v>
@@ -4787,10 +4790,10 @@
         <v>32</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G18" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H18" s="0" t="s">
         <v>22</v>
@@ -4819,7 +4822,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>34</v>
@@ -4831,10 +4834,10 @@
         <v>36</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H19" s="0" t="s">
         <v>22</v>
@@ -4863,7 +4866,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>38</v>
@@ -4875,10 +4878,10 @@
         <v>40</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H20" s="0" t="s">
         <v>22</v>
@@ -4907,7 +4910,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>42</v>
@@ -4919,10 +4922,10 @@
         <v>44</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H21" s="0" t="s">
         <v>22</v>
@@ -4951,7 +4954,7 @@
         <v>15</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>46</v>
@@ -4963,10 +4966,10 @@
         <v>48</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H22" s="0" t="s">
         <v>22</v>
@@ -4995,22 +4998,22 @@
         <v>15</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>50</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H23" s="0" t="s">
         <v>22</v>
@@ -5039,29 +5042,29 @@
         <v>15</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="E24" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="F24" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="H24" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="F24" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="G24" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="H24" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="I24" s="0" t="s">
-        <v>53</v>
-      </c>
       <c r="J24" s="0" t="s">
         <v>23</v>
       </c>
@@ -5072,10 +5075,10 @@
         <v>24</v>
       </c>
       <c r="M24" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N24" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25">
@@ -5083,29 +5086,29 @@
         <v>15</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="E25" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="F25" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="G25" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="H25" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="I25" s="0" t="s">
         <v>58</v>
       </c>
-      <c r="F25" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="G25" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="H25" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="I25" s="0" t="s">
-        <v>56</v>
-      </c>
       <c r="J25" s="0" t="s">
         <v>23</v>
       </c>
@@ -5116,10 +5119,10 @@
         <v>24</v>
       </c>
       <c r="M25" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N25" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26">
@@ -5127,29 +5130,29 @@
         <v>15</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D26" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="F26" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="H26" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="I26" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="E26" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="F26" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="G26" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="H26" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="I26" s="0" t="s">
-        <v>60</v>
-      </c>
       <c r="J26" s="0" t="s">
         <v>23</v>
       </c>
@@ -5160,10 +5163,10 @@
         <v>24</v>
       </c>
       <c r="M26" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N26" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27">
@@ -5171,29 +5174,29 @@
         <v>15</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D27" s="0" t="s">
         <v>43</v>
       </c>
       <c r="E27" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="F27" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="G27" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="H27" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="I27" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="F27" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="G27" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="H27" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="I27" s="0" t="s">
-        <v>64</v>
-      </c>
       <c r="J27" s="0" t="s">
         <v>23</v>
       </c>
@@ -5204,10 +5207,10 @@
         <v>24</v>
       </c>
       <c r="M27" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N27" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28">
@@ -5215,29 +5218,29 @@
         <v>15</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E28" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="F28" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="G28" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="H28" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="F28" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="G28" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="H28" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="I28" s="0" t="s">
-        <v>67</v>
-      </c>
       <c r="J28" s="0" t="s">
         <v>23</v>
       </c>
@@ -5248,10 +5251,10 @@
         <v>24</v>
       </c>
       <c r="M28" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N28" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29">
@@ -5259,28 +5262,28 @@
         <v>15</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D29" s="0" t="s">
         <v>27</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G29" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H29" s="0" t="s">
         <v>22</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J29" s="0" t="s">
         <v>23</v>
@@ -5292,10 +5295,10 @@
         <v>24</v>
       </c>
       <c r="M29" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="N29" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30">
@@ -5303,7 +5306,7 @@
         <v>15</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>17</v>
@@ -5315,10 +5318,10 @@
         <v>19</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H30" s="0" t="s">
         <v>22</v>
@@ -5327,7 +5330,7 @@
         <v>17</v>
       </c>
       <c r="J30" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K30" s="0" t="s">
         <v>24</v>
@@ -5347,7 +5350,7 @@
         <v>15</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>26</v>
@@ -5359,10 +5362,10 @@
         <v>28</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H31" s="0" t="s">
         <v>22</v>
@@ -5371,7 +5374,7 @@
         <v>26</v>
       </c>
       <c r="J31" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K31" s="0" t="s">
         <v>24</v>
@@ -5391,7 +5394,7 @@
         <v>15</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>30</v>
@@ -5403,10 +5406,10 @@
         <v>32</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G32" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H32" s="0" t="s">
         <v>22</v>
@@ -5415,7 +5418,7 @@
         <v>30</v>
       </c>
       <c r="J32" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K32" s="0" t="s">
         <v>24</v>
@@ -5435,7 +5438,7 @@
         <v>15</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>34</v>
@@ -5447,10 +5450,10 @@
         <v>36</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G33" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H33" s="0" t="s">
         <v>22</v>
@@ -5459,7 +5462,7 @@
         <v>34</v>
       </c>
       <c r="J33" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K33" s="0" t="s">
         <v>24</v>
@@ -5479,7 +5482,7 @@
         <v>15</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>38</v>
@@ -5491,10 +5494,10 @@
         <v>40</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G34" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H34" s="0" t="s">
         <v>22</v>
@@ -5503,7 +5506,7 @@
         <v>38</v>
       </c>
       <c r="J34" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K34" s="0" t="s">
         <v>24</v>
@@ -5523,7 +5526,7 @@
         <v>15</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>42</v>
@@ -5535,10 +5538,10 @@
         <v>44</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G35" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H35" s="0" t="s">
         <v>22</v>
@@ -5547,7 +5550,7 @@
         <v>42</v>
       </c>
       <c r="J35" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K35" s="0" t="s">
         <v>24</v>
@@ -5567,7 +5570,7 @@
         <v>15</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>46</v>
@@ -5579,10 +5582,10 @@
         <v>48</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G36" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H36" s="0" t="s">
         <v>22</v>
@@ -5591,7 +5594,7 @@
         <v>30</v>
       </c>
       <c r="J36" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K36" s="0" t="s">
         <v>24</v>
@@ -5611,22 +5614,22 @@
         <v>15</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C37" s="0" t="s">
         <v>50</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F37" s="0" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G37" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H37" s="0" t="s">
         <v>22</v>
@@ -5635,7 +5638,7 @@
         <v>50</v>
       </c>
       <c r="J37" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K37" s="0" t="s">
         <v>24</v>
@@ -5655,31 +5658,31 @@
         <v>15</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="E38" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="F38" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="G38" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="H38" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="I38" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="F38" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="G38" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="H38" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="I38" s="0" t="s">
-        <v>53</v>
-      </c>
       <c r="J38" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K38" s="0" t="s">
         <v>24</v>
@@ -5688,10 +5691,10 @@
         <v>24</v>
       </c>
       <c r="M38" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N38" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="39">
@@ -5699,31 +5702,31 @@
         <v>15</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="E39" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="F39" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="G39" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="H39" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="I39" s="0" t="s">
         <v>58</v>
       </c>
-      <c r="F39" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="G39" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="H39" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="I39" s="0" t="s">
-        <v>56</v>
-      </c>
       <c r="J39" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K39" s="0" t="s">
         <v>24</v>
@@ -5732,10 +5735,10 @@
         <v>24</v>
       </c>
       <c r="M39" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N39" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40">
@@ -5743,31 +5746,31 @@
         <v>15</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D40" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="E40" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="F40" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="G40" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="H40" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="E40" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="F40" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="G40" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="H40" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="I40" s="0" t="s">
-        <v>60</v>
-      </c>
       <c r="J40" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K40" s="0" t="s">
         <v>24</v>
@@ -5776,10 +5779,10 @@
         <v>24</v>
       </c>
       <c r="M40" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N40" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="41">
@@ -5787,31 +5790,31 @@
         <v>15</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D41" s="0" t="s">
         <v>43</v>
       </c>
       <c r="E41" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="F41" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="G41" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="H41" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="I41" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="F41" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="G41" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="H41" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="I41" s="0" t="s">
-        <v>64</v>
-      </c>
       <c r="J41" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K41" s="0" t="s">
         <v>24</v>
@@ -5820,10 +5823,10 @@
         <v>24</v>
       </c>
       <c r="M41" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N41" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42">
@@ -5831,31 +5834,31 @@
         <v>15</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E42" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="F42" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="G42" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="H42" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="I42" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="F42" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="G42" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="H42" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="I42" s="0" t="s">
-        <v>67</v>
-      </c>
       <c r="J42" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K42" s="0" t="s">
         <v>24</v>
@@ -5864,10 +5867,10 @@
         <v>24</v>
       </c>
       <c r="M42" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N42" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43">
@@ -5875,31 +5878,31 @@
         <v>15</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D43" s="0" t="s">
         <v>27</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H43" s="0" t="s">
         <v>22</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J43" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K43" s="0" t="s">
         <v>24</v>
@@ -5908,10 +5911,10 @@
         <v>24</v>
       </c>
       <c r="M43" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="N43" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44">
@@ -5919,7 +5922,7 @@
         <v>15</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C44" s="0" t="s">
         <v>17</v>
@@ -5931,10 +5934,10 @@
         <v>19</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H44" s="0" t="s">
         <v>22</v>
@@ -5963,7 +5966,7 @@
         <v>15</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C45" s="0" t="s">
         <v>26</v>
@@ -5975,10 +5978,10 @@
         <v>28</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H45" s="0" t="s">
         <v>22</v>
@@ -6007,7 +6010,7 @@
         <v>15</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C46" s="0" t="s">
         <v>30</v>
@@ -6019,10 +6022,10 @@
         <v>32</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H46" s="0" t="s">
         <v>22</v>
@@ -6051,7 +6054,7 @@
         <v>15</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C47" s="0" t="s">
         <v>34</v>
@@ -6063,10 +6066,10 @@
         <v>36</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H47" s="0" t="s">
         <v>22</v>
@@ -6095,7 +6098,7 @@
         <v>15</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C48" s="0" t="s">
         <v>38</v>
@@ -6107,10 +6110,10 @@
         <v>40</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G48" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H48" s="0" t="s">
         <v>22</v>
@@ -6139,7 +6142,7 @@
         <v>15</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C49" s="0" t="s">
         <v>42</v>
@@ -6151,10 +6154,10 @@
         <v>44</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G49" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H49" s="0" t="s">
         <v>22</v>
@@ -6183,7 +6186,7 @@
         <v>15</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C50" s="0" t="s">
         <v>46</v>
@@ -6195,10 +6198,10 @@
         <v>48</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G50" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H50" s="0" t="s">
         <v>22</v>
@@ -6227,22 +6230,22 @@
         <v>15</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C51" s="0" t="s">
         <v>50</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G51" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H51" s="0" t="s">
         <v>22</v>
@@ -6271,29 +6274,29 @@
         <v>15</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="E52" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="F52" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="G52" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="H52" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="I52" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="F52" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="G52" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="H52" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="I52" s="0" t="s">
-        <v>53</v>
-      </c>
       <c r="J52" s="0" t="s">
         <v>23</v>
       </c>
@@ -6304,10 +6307,10 @@
         <v>24</v>
       </c>
       <c r="M52" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N52" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53">
@@ -6315,29 +6318,29 @@
         <v>15</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="E53" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="F53" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="G53" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="H53" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="I53" s="0" t="s">
         <v>58</v>
       </c>
-      <c r="F53" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="G53" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="H53" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="I53" s="0" t="s">
-        <v>56</v>
-      </c>
       <c r="J53" s="0" t="s">
         <v>23</v>
       </c>
@@ -6348,10 +6351,10 @@
         <v>24</v>
       </c>
       <c r="M53" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N53" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54">
@@ -6359,29 +6362,29 @@
         <v>15</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D54" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="E54" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="F54" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="G54" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="H54" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="I54" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="E54" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="F54" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="G54" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="H54" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="I54" s="0" t="s">
-        <v>60</v>
-      </c>
       <c r="J54" s="0" t="s">
         <v>23</v>
       </c>
@@ -6392,10 +6395,10 @@
         <v>24</v>
       </c>
       <c r="M54" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N54" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="55">
@@ -6403,29 +6406,29 @@
         <v>15</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D55" s="0" t="s">
         <v>43</v>
       </c>
       <c r="E55" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="F55" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="G55" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="H55" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="I55" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="F55" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="G55" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="H55" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="I55" s="0" t="s">
-        <v>64</v>
-      </c>
       <c r="J55" s="0" t="s">
         <v>23</v>
       </c>
@@ -6436,10 +6439,10 @@
         <v>24</v>
       </c>
       <c r="M55" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N55" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="56">
@@ -6447,29 +6450,29 @@
         <v>15</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E56" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="F56" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="G56" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="H56" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="I56" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="F56" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="G56" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="H56" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="I56" s="0" t="s">
-        <v>67</v>
-      </c>
       <c r="J56" s="0" t="s">
         <v>23</v>
       </c>
@@ -6480,10 +6483,10 @@
         <v>24</v>
       </c>
       <c r="M56" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N56" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57">
@@ -6491,28 +6494,28 @@
         <v>15</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D57" s="0" t="s">
         <v>27</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H57" s="0" t="s">
         <v>22</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J57" s="0" t="s">
         <v>23</v>
@@ -6524,42 +6527,42 @@
         <v>24</v>
       </c>
       <c r="M57" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="N57" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C58" s="0" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G58" s="0" t="s">
         <v>21</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I58" s="0" t="s">
         <v>50</v>
       </c>
       <c r="J58" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K58" s="0" t="s">
         <v>24</v>
@@ -6576,34 +6579,34 @@
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C59" s="0" t="s">
         <v>50</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F59" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="G59" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="H59" s="0" t="s">
         <v>90</v>
-      </c>
-      <c r="G59" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="H59" s="0" t="s">
-        <v>88</v>
       </c>
       <c r="I59" s="0" t="s">
         <v>50</v>
       </c>
       <c r="J59" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K59" s="0" t="s">
         <v>24</v>
@@ -6620,34 +6623,34 @@
     </row>
     <row r="60">
       <c r="A60" s="0" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C60" s="0" t="s">
         <v>50</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I60" s="0" t="s">
         <v>50</v>
       </c>
       <c r="J60" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K60" s="0" t="s">
         <v>24</v>
@@ -6664,34 +6667,34 @@
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C61" s="0" t="s">
         <v>50</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I61" s="0" t="s">
         <v>50</v>
       </c>
       <c r="J61" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K61" s="0" t="s">
         <v>24</v>
@@ -6708,28 +6711,28 @@
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C62" s="0" t="s">
         <v>38</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G62" s="0" t="s">
         <v>21</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I62" s="0" t="s">
         <v>38</v>
@@ -6752,28 +6755,28 @@
     </row>
     <row r="63">
       <c r="A63" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C63" s="0" t="s">
         <v>46</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E63" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="F63" s="0" t="s">
         <v>100</v>
-      </c>
-      <c r="F63" s="0" t="s">
-        <v>98</v>
       </c>
       <c r="G63" s="0" t="s">
         <v>21</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I63" s="0" t="s">
         <v>30</v>
@@ -6796,31 +6799,31 @@
     </row>
     <row r="64">
       <c r="A64" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G64" s="0" t="s">
         <v>21</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J64" s="0" t="s">
         <v>23</v>
@@ -6832,36 +6835,36 @@
         <v>24</v>
       </c>
       <c r="M64" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N64" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C65" s="0" t="s">
         <v>38</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G65" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I65" s="0" t="s">
         <v>38</v>
@@ -6884,28 +6887,28 @@
     </row>
     <row r="66">
       <c r="A66" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C66" s="0" t="s">
         <v>46</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G66" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I66" s="0" t="s">
         <v>30</v>
@@ -6928,31 +6931,31 @@
     </row>
     <row r="67">
       <c r="A67" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B67" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="C67" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="D67" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="E67" s="0" t="s">
         <v>103</v>
       </c>
-      <c r="C67" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="D67" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="E67" s="0" t="s">
-        <v>102</v>
-      </c>
       <c r="F67" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G67" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J67" s="0" t="s">
         <v>23</v>
@@ -6964,42 +6967,42 @@
         <v>24</v>
       </c>
       <c r="M67" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N67" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C68" s="0" t="s">
         <v>38</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I68" s="0" t="s">
         <v>38</v>
       </c>
       <c r="J68" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K68" s="0" t="s">
         <v>24</v>
@@ -7016,34 +7019,34 @@
     </row>
     <row r="69">
       <c r="A69" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C69" s="0" t="s">
         <v>46</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G69" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I69" s="0" t="s">
         <v>30</v>
       </c>
       <c r="J69" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K69" s="0" t="s">
         <v>24</v>
@@ -7060,34 +7063,34 @@
     </row>
     <row r="70">
       <c r="A70" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I70" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J70" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K70" s="0" t="s">
         <v>24</v>
@@ -7096,42 +7099,42 @@
         <v>24</v>
       </c>
       <c r="M70" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N70" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C71" s="0" t="s">
         <v>38</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I71" s="0" t="s">
         <v>38</v>
       </c>
       <c r="J71" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K71" s="0" t="s">
         <v>24</v>
@@ -7148,34 +7151,34 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C72" s="0" t="s">
         <v>46</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I72" s="0" t="s">
         <v>30</v>
       </c>
       <c r="J72" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K72" s="0" t="s">
         <v>24</v>
@@ -7192,34 +7195,34 @@
     </row>
     <row r="73">
       <c r="A73" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G73" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J73" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K73" s="0" t="s">
         <v>24</v>
@@ -7228,42 +7231,42 @@
         <v>24</v>
       </c>
       <c r="M73" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N73" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C74" s="0" t="s">
         <v>38</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I74" s="0" t="s">
         <v>38</v>
       </c>
       <c r="J74" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K74" s="0" t="s">
         <v>24</v>
@@ -7280,34 +7283,34 @@
     </row>
     <row r="75">
       <c r="A75" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C75" s="0" t="s">
         <v>46</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G75" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I75" s="0" t="s">
         <v>30</v>
       </c>
       <c r="J75" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K75" s="0" t="s">
         <v>24</v>
@@ -7324,34 +7327,34 @@
     </row>
     <row r="76">
       <c r="A76" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J76" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K76" s="0" t="s">
         <v>24</v>
@@ -7360,10 +7363,10 @@
         <v>24</v>
       </c>
       <c r="M76" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N76" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
